--- a/selenium/data/test_data.xlsx
+++ b/selenium/data/test_data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\nykaa\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Wipro_capstone_project\selenium\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
